--- a/final_data_pipeline/output/311225_elec_options.xlsx
+++ b/final_data_pipeline/output/311225_elec_options.xlsx
@@ -1667,7 +1667,7 @@
         <v>46</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE12">
         <v>8000</v>
@@ -1762,7 +1762,7 @@
         <v>46</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE13">
         <v>8000</v>
@@ -1857,7 +1857,7 @@
         <v>46</v>
       </c>
       <c r="AD14">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE14">
         <v>8000</v>
@@ -1952,7 +1952,7 @@
         <v>46</v>
       </c>
       <c r="AD15">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE15">
         <v>8000</v>
@@ -2047,7 +2047,7 @@
         <v>46</v>
       </c>
       <c r="AD16">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE16">
         <v>8000</v>
